--- a/technology_surveys/019_social_media_activism_fatigue_study--technology_surveys.xlsx
+++ b/technology_surveys/019_social_media_activism_fatigue_study--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_hour'}</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 hour'}</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_hours'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '1-2 hours'}</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'2-4_hours'}</t>
+          <t>2-4_hours</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '2-4 hours'}</t>
+          <t>2-4 hours</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'4-6_hours'}</t>
+          <t>4-6_hours</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '4-6 hours'}</t>
+          <t>4-6 hours</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_6_hours'}</t>
+          <t>more_than_6_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'More than 6 hours'}</t>
+          <t>More than 6 hours</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'informational_content'}</t>
+          <t>informational_content</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Informational content'}</t>
+          <t>Informational content</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'advocacy_content'}</t>
+          <t>advocacy_content</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Advocacy content'}</t>
+          <t>Advocacy content</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment_content'}</t>
+          <t>entertainment_content</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment content'}</t>
+          <t>Entertainment content</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'1-5_times'}</t>
+          <t>1-5_times</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': '1-5 times'}</t>
+          <t>1-5 times</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'5-20_times'}</t>
+          <t>5-20_times</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': '5-20 times'}</t>
+          <t>5-20 times</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_20_times'}</t>
+          <t>more_than_20_times</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'More than 20 times'}</t>
+          <t>More than 20 times</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'research'}</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Research'}</t>
+          <t>Research</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'awareness'}</t>
+          <t>awareness</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Awareness'}</t>
+          <t>Awareness</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'advocacy'}</t>
+          <t>advocacy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Advocacy'}</t>
+          <t>Advocacy</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'fundraising'}</t>
+          <t>fundraising</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Fundraising'}</t>
+          <t>Fundraising</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'informative'}</t>
+          <t>informative</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Informative'}</t>
+          <t>Informative</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'emotional'}</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional'}</t>
+          <t>Emotional</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'rational'}</t>
+          <t>rational</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Rational'}</t>
+          <t>Rational</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1/3'}</t>
+          <t>less_than_1/3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1/3'}</t>
+          <t>Less than 1/3</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'1/3_to_1/2'}</t>
+          <t>1/3_to_1/2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': '1/3 to 1/2'}</t>
+          <t>1/3 to 1/2</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'1/2_to_2/3'}</t>
+          <t>1/2_to_2/3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': '1/2 to 2/3'}</t>
+          <t>1/2 to 2/3</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'2/3_or_more'}</t>
+          <t>2/3_or_more</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': '2/3 or more'}</t>
+          <t>2/3 or more</t>
         </is>
       </c>
     </row>
